--- a/allUniversity/AllUniversity.xlsx
+++ b/allUniversity/AllUniversity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\allUniversity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50198D4A-93C3-4946-B33B-54E67148F56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373D060A-1316-4FD3-9DAD-E00D0C2EF7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>university</t>
   </si>
@@ -51,9 +51,6 @@
     <t>scholarship  requirement</t>
   </si>
   <si>
-    <t>English</t>
-  </si>
-  <si>
     <t>country expences</t>
   </si>
   <si>
@@ -70,13 +67,64 @@
   </si>
   <si>
     <t>e-mail</t>
+  </si>
+  <si>
+    <t>Universität Heidelberg</t>
+  </si>
+  <si>
+    <t>germany</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>500eur</t>
+  </si>
+  <si>
+    <t>languge</t>
+  </si>
+  <si>
+    <t>german</t>
+  </si>
+  <si>
+    <t>computer scince</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>302eur</t>
+  </si>
+  <si>
+    <t>01.06. – 30.09.</t>
+  </si>
+  <si>
+    <t>languge profecency</t>
+  </si>
+  <si>
+    <t>Freie Universitaet Berlin</t>
+  </si>
+  <si>
+    <t> June 1, 2024, through July 15, 2024</t>
+  </si>
+  <si>
+    <t>Computer Engineering  &amp; Information Systems Management</t>
+  </si>
+  <si>
+    <t>GERMANY</t>
+  </si>
+  <si>
+    <t>Technische Universität Berlin (TU Berlin)</t>
+  </si>
+  <si>
+    <t>KIT, Karlsruhe Institute of Technology</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +138,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -130,7 +184,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -153,11 +207,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -176,6 +267,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -461,16 +573,22 @@
   <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="29.21875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="11"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -486,10 +604,18 @@
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="B2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -506,9 +632,15 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="12">
+        <v>84</v>
+      </c>
+      <c r="C3" s="13">
+        <v>97</v>
+      </c>
+      <c r="D3" s="12">
+        <v>147</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -526,9 +658,15 @@
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -544,11 +682,17 @@
     </row>
     <row r="5" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -564,11 +708,11 @@
     </row>
     <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -584,11 +728,11 @@
     </row>
     <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -604,11 +748,17 @@
     </row>
     <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>19</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -626,9 +776,15 @@
       <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -644,11 +800,15 @@
     </row>
     <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="12"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -666,9 +826,13 @@
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="12"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -686,9 +850,15 @@
       <c r="A12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="12">
+        <v>606</v>
+      </c>
+      <c r="D12" s="12">
+        <v>600</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -706,9 +876,15 @@
       <c r="A13" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -726,9 +902,15 @@
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -744,11 +926,17 @@
     </row>
     <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="14">
+        <v>45627</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -764,11 +952,11 @@
     </row>
     <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -783,6 +971,9 @@
       <c r="P16" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/allUniversity/AllUniversity.xlsx
+++ b/allUniversity/AllUniversity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\allUniversity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373D060A-1316-4FD3-9DAD-E00D0C2EF7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B4297F-3D96-4FD6-A587-4A5C5FC277FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>university</t>
   </si>
@@ -42,9 +42,6 @@
     <t xml:space="preserve">scholarship </t>
   </si>
   <si>
-    <t>country</t>
-  </si>
-  <si>
     <t>requirement</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>Universität Heidelberg</t>
   </si>
   <si>
-    <t>germany</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
@@ -118,13 +112,40 @@
   </si>
   <si>
     <t>KIT, Karlsruhe Institute of Technology</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering(E) &amp; Mechatronics and Information Technology(G) &amp; informatics(G)</t>
+  </si>
+  <si>
+    <t>SAT 1200 &amp; toefl 88</t>
+  </si>
+  <si>
+    <t>english &amp; german</t>
+  </si>
+  <si>
+    <t>ireland</t>
+  </si>
+  <si>
+    <t>Trinity College Dublin, The University of Dublin</t>
+  </si>
+  <si>
+    <t>english</t>
+  </si>
+  <si>
+    <t>assesment and Alevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assesment </t>
+  </si>
+  <si>
+    <t>November 1st -  June 30th</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +165,16 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="7">
@@ -248,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -278,17 +309,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -570,25 +602,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="29.21875" style="8" customWidth="1"/>
     <col min="3" max="3" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5546875" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
-      <c r="F1" s="11"/>
+      <c r="F1" s="11" t="s">
+        <v>32</v>
+      </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -600,24 +635,26 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="12"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -635,15 +672,19 @@
       <c r="B3" s="12">
         <v>84</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="8">
         <v>97</v>
       </c>
       <c r="D3" s="12">
         <v>147</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12">
+        <v>89</v>
+      </c>
+      <c r="G3" s="12">
+        <v>126</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -656,7 +697,7 @@
     </row>
     <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>15</v>
@@ -667,9 +708,9 @@
       <c r="D4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -682,20 +723,14 @@
     </row>
     <row r="5" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -713,9 +748,9 @@
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -727,15 +762,25 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="12"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -746,22 +791,26 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>19</v>
-      </c>
       <c r="C8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="12"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -774,20 +823,20 @@
     </row>
     <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="12"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -800,18 +849,22 @@
     </row>
     <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="E10" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="12"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -823,19 +876,23 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>6</v>
+      <c r="A11" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C11" s="12">
+        <v>606</v>
+      </c>
+      <c r="D11" s="12">
+        <v>600</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12">
+        <v>21000</v>
+      </c>
+      <c r="G11" s="12"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -848,20 +905,22 @@
     </row>
     <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="12">
-        <v>606</v>
-      </c>
-      <c r="D12" s="12">
-        <v>600</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12">
+        <v>5000</v>
+      </c>
+      <c r="G12" s="12"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -874,20 +933,22 @@
     </row>
     <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="12"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -899,21 +960,25 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>7</v>
+      <c r="A14" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="D14" s="13">
+        <v>45627</v>
+      </c>
+      <c r="E14" s="15">
+        <v>45306</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="12"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -928,18 +993,12 @@
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="14">
-        <v>45627</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -950,29 +1009,9 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/allUniversity/AllUniversity.xlsx
+++ b/allUniversity/AllUniversity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\allUniversity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B4297F-3D96-4FD6-A587-4A5C5FC277FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190DC179-3DC0-4270-97EF-DA08E2F9EBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
   <si>
     <t>university</t>
   </si>
@@ -139,13 +139,46 @@
   </si>
   <si>
     <t>November 1st -  June 30th</t>
+  </si>
+  <si>
+    <t>QATAR</t>
+  </si>
+  <si>
+    <t>qatar university</t>
+  </si>
+  <si>
+    <t>computer scince and engineering</t>
+  </si>
+  <si>
+    <t>above 70% high school</t>
+  </si>
+  <si>
+    <t>12280$</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> talent scholership: above 80% high school , talent in technology, 2 recommendation letter, </t>
+  </si>
+  <si>
+    <t>yes-full fee , books , monthly 1000qar , dorm, airplane, transportatio</t>
+  </si>
+  <si>
+    <t>no need for mat ig SAT more than 598</t>
+  </si>
+  <si>
+    <t>QUMCC@qu.edu.qa</t>
+  </si>
+  <si>
+    <t>Hamad bin Khalifa University</t>
+  </si>
+  <si>
+    <t>computer engineering &amp; cybersecurity</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +208,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -276,10 +317,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -303,27 +345,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -602,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -611,21 +666,25 @@
     <col min="4" max="4" width="25.5546875" customWidth="1"/>
     <col min="5" max="5" width="29.109375" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="78.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="11" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="G1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="18"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -635,27 +694,31 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="1"/>
+      <c r="G2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -669,23 +732,25 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="9">
         <v>84</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>97</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="9">
         <v>147</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12">
+      <c r="E3" s="9"/>
+      <c r="F3" s="9">
         <v>89</v>
       </c>
-      <c r="G3" s="12">
-        <v>126</v>
-      </c>
-      <c r="H3" s="1"/>
+      <c r="G3" s="9">
+        <v>122</v>
+      </c>
+      <c r="H3" s="1">
+        <v>183</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -699,18 +764,18 @@
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -725,12 +790,12 @@
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -745,12 +810,12 @@
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -765,23 +830,27 @@
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="1"/>
+      <c r="G7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -791,27 +860,31 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="1"/>
+      <c r="G8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -825,19 +898,23 @@
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="s">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="1"/>
+      <c r="G9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -851,20 +928,22 @@
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="12"/>
+      <c r="G10" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -879,20 +958,22 @@
       <c r="A11" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="9">
         <v>606</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="9">
         <v>600</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9">
         <v>21000</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -907,20 +988,22 @@
       <c r="A12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12">
+      <c r="E12" s="9"/>
+      <c r="F12" s="9">
         <v>5000</v>
       </c>
-      <c r="G12" s="12"/>
+      <c r="G12" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -935,20 +1018,22 @@
       <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12" t="s">
+      <c r="E13" s="9"/>
+      <c r="F13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="12"/>
+      <c r="G13" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -963,22 +1048,22 @@
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <v>45627</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="13">
         <v>45306</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="12"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -993,12 +1078,14 @@
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="19" t="s">
+        <v>46</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1009,10 +1096,20 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G16" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G15" r:id="rId1" display="mailto:QUMCC@qu.edu.qa" xr:uid="{ABCED68B-E591-42A7-A247-4D87E5BB3872}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/allUniversity/AllUniversity.xlsx
+++ b/allUniversity/AllUniversity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\allUniversity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\AllUniversity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190DC179-3DC0-4270-97EF-DA08E2F9EBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D02893-E77A-4DD7-AD33-C2CC4DF44074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -360,22 +360,22 @@
     <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -658,33 +658,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="29.21875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5546875" customWidth="1"/>
-    <col min="5" max="5" width="29.109375" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.140625" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="78.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="78.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="18"/>
+      <c r="H1" s="19"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -694,7 +694,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -728,7 +728,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -760,7 +760,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -786,7 +786,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -806,7 +806,7 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -826,7 +826,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
@@ -860,7 +860,7 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
@@ -894,7 +894,7 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -924,7 +924,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -954,7 +954,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>2</v>
       </c>
@@ -984,7 +984,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>4</v>
       </c>
@@ -1014,7 +1014,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
@@ -1044,7 +1044,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
@@ -1074,7 +1074,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
@@ -1083,7 +1083,7 @@
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="15" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="1"/>
@@ -1096,7 +1096,7 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G16" s="9" t="s">
         <v>45</v>
       </c>
